--- a/artfynd/A 39119-2024 artfynd.xlsx
+++ b/artfynd/A 39119-2024 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>267861</v>
       </c>
       <c r="B3" t="n">
-        <v>96679</v>
+        <v>96682</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>1003880</v>
       </c>
       <c r="B5" t="n">
-        <v>96820</v>
+        <v>96823</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39119-2024 artfynd.xlsx
+++ b/artfynd/A 39119-2024 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>267861</v>
       </c>
       <c r="B3" t="n">
-        <v>96682</v>
+        <v>96683</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>1003880</v>
       </c>
       <c r="B5" t="n">
-        <v>96823</v>
+        <v>96824</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39119-2024 artfynd.xlsx
+++ b/artfynd/A 39119-2024 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>267861</v>
       </c>
       <c r="B3" t="n">
-        <v>96683</v>
+        <v>96688</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>1003880</v>
       </c>
       <c r="B5" t="n">
-        <v>96824</v>
+        <v>96829</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
